--- a/output/pdf_financials_xlsx/GXP.xlsx
+++ b/output/pdf_financials_xlsx/GXP.xlsx
@@ -1925,10 +1925,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.074734</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.824447</v>
       </c>
     </row>
     <row r="93">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-2.490887</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>3.386167</v>
+        <v>1.420159</v>
       </c>
     </row>
     <row r="119">
@@ -3283,7 +3283,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3661,7 +3665,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -4291,7 +4299,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GXP.xlsx
+++ b/output/pdf_financials_xlsx/GXP.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.017568</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.752608</v>
+        <v>2.856101</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.192161</v>
+        <v>2.143055</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.017568</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-1.752608</v>
+        <v>-2.856101</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.192161</v>
+        <v>-2.143055</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002993</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.014123</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.044889</v>
       </c>
     </row>
     <row r="13">
@@ -863,13 +863,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.014575</v>
+        <v>-0.017568</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.850059</v>
+        <v>-2.864182</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.850059</v>
+        <v>-2.894948</v>
       </c>
     </row>
     <row r="28">
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.014575</v>
+        <v>-0.017568</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.850059</v>
+        <v>-2.864182</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.822377</v>
+        <v>-2.867266</v>
       </c>
     </row>
     <row r="30">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">

--- a/output/pdf_financials_xlsx/GXP.xlsx
+++ b/output/pdf_financials_xlsx/GXP.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.752608</v>
+        <v>1.753513</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.192161</v>
+        <v>1.265612</v>
       </c>
     </row>
     <row r="8">
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.008007999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -2321,7 +2321,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.159676</v>
       </c>
     </row>
     <row r="116">
@@ -3849,7 +3849,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -4268,7 +4272,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -5156,7 +5164,11 @@
           <t>Proceeds from private placement 4,251,253</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -5713,7 +5725,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
         <v>0.0002</v>
       </c>
